--- a/out/LSTM-Mamba1_repeat_2_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.173053370802809</v>
+        <v>15.28973846592426</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.1742763026941591</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.544994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.944994382064366</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001443642544040922</v>
+        <v>-9.028927320521324e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1658468005994191</v>
+        <v>-0.1037250332593648</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1038153225325701</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1660498872639093</v>
+        <v>-0.1038953169789104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2111524131920476</v>
+        <v>0.2876418110555966</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2566603594856511</v>
+        <v>0.4719405879425919</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01504456510723385</v>
+        <v>0.02049438205934407</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.07525836486090882</v>
+        <v>0.2248262053035155</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02638304119711482</v>
+        <v>0.03594029158310495</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.112974861427176</v>
+        <v>0.2762054937622342</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03205227924205539</v>
+        <v>0.04366320975871988</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1506938683538078</v>
+        <v>0.3275882019587611</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.00848032215218711</v>
+        <v>0.01155418788124789</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.135562990521807</v>
+        <v>0.3069779783840266</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004709312534274701</v>
+        <v>0.006417104351165654</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.136494594845173</v>
+        <v>0.3082488606887963</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.009898579598035839</v>
+        <v>0.01348698945083388</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1515887497141231</v>
+        <v>0.3288123602160108</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.00388617955492248</v>
+        <v>0.005294658180000239</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1494532111534595</v>
+        <v>0.3259053062485033</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002765245827088388</v>
+        <v>0.003769158075759273</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1510976279799475</v>
+        <v>0.3281472705010839</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001085386632673013</v>
+        <v>0.001480532971537081</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1505006319084733</v>
+        <v>0.3273358735346063</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006146480931378066</v>
+        <v>0.0008381530023541796</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1506425474028008</v>
+        <v>0.3275309646785506</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002310482153670261</v>
+        <v>0.0003167771692067918</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1504895003816341</v>
+        <v>0.3273241493362637</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001050960443416172</v>
+        <v>0.0001458315807480156</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1504695780567941</v>
+        <v>0.3272988064421003</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.536626471769872e-05</v>
+        <v>4.989812001607026e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1504348281991135</v>
+        <v>0.3272534524713112</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1504129420253157</v>
+        <v>0.3272256063400598</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.200814771567029e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1504079323449694</v>
+        <v>0.3272205936811452</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-3.767886923740136e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1504034053429216</v>
+        <v>0.3272162480553358</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1503996885124419</v>
+        <v>0.3272128977005431</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1503943926824378</v>
+        <v>0.3272075283735553</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1503887306854341</v>
+        <v>0.3272015356401249</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>0</v>
+        <v>-4.890058184668745e-06</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1503885469429749</v>
+        <v>0.3271961678515465</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1503885836914666</v>
+        <v>0.3271962046000382</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1503886939369422</v>
+        <v>0.3271963148455138</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1503887674339258</v>
+        <v>0.3271963883424974</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1503889511763849</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1503904946130414</v>
+        <v>0.327198115521613</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1503919645527145</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1503932140014365</v>
+        <v>0.3272008349100081</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1503945736956338</v>
+        <v>0.3272021946042054</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1503923687861245</v>
+        <v>0.3271999896946962</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1503919645527145</v>
+        <v>0.3271995854612861</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1503911193374025</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1503916705647798</v>
+        <v>0.3271992914733514</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1503913398283534</v>
+        <v>0.327198960736925</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1503910458404189</v>
+        <v>0.3271986667489906</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1503911193374025</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1503906783555006</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.150390568110025</v>
+        <v>0.3271981890185967</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1503905313615333</v>
+        <v>0.327198152270105</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1503906783555006</v>
+        <v>0.3271982992640722</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1503902006251069</v>
+        <v>0.3271978215336785</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1503911560858942</v>
+        <v>0.3271987769944659</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1503911193374025</v>
+        <v>0.3271987402459742</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1503907886009761</v>
+        <v>0.3271984095095478</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1503912295828781</v>
+        <v>0.3271988504914497</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1503906048585169</v>
+        <v>0.3271982257670886</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1503904211160578</v>
+        <v>0.3271980420246294</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1503900168826477</v>
+        <v>0.3271976377912194</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1503891716673358</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1503891349188441</v>
+        <v>0.3271967558274158</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1503892819128113</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1503892084158277</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1503892819128113</v>
+        <v>0.327196902821383</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1503893186613033</v>
+        <v>0.3271969395698749</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1503892084158277</v>
+        <v>0.3271968293243994</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1503896493977297</v>
+        <v>0.3271972703063013</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1503895391522541</v>
+        <v>0.3271971600608258</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1503895024037622</v>
+        <v>0.3271971233123338</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1503894289067786</v>
+        <v>0.3271970498153502</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1503893921582869</v>
+        <v>0.3271970130668585</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1503891716673358</v>
+        <v>0.3271967925759074</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1503890981703522</v>
+        <v>0.3271967190789238</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1503890246733685</v>
+        <v>0.3271966455819402</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1503890614218605</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1503889511763849</v>
+        <v>0.3271965720849566</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1503890614218605</v>
+        <v>0.3271966823304321</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.4257236973058409</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.150389355409795</v>
+        <v>0.3271969763183666</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.0740314606762852</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>2.544994382064366</v>
+        <v>0.9867280899030685</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.544994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.944994382064366</v>
+        <v>1.699424719129852</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.944994382064366</v>
+        <v>1.499424719129852</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.944994382064366</v>
+        <v>0.7867280899030684</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001443642544040922</v>
+        <v>-0.0001179446991757723</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1658468005994191</v>
+        <v>-0.1354958059853739</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.173053370802809</v>
+        <v>0.0740314606762852</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1659911648538233</v>
+        <v>-0.1356137506845497</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1660498872639093</v>
+        <v>-0.1356862638100479</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2111524131920476</v>
+        <v>0.2607404283618791</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.2566603594856511</v>
+        <v>0.3862957385630379</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01504456510723385</v>
+        <v>0.01857770077678691</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.07525836486090882</v>
+        <v>0.1622920145064818</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.02638304119711482</v>
+        <v>0.03257908566728022</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.112974861427176</v>
+        <v>0.2088662120571597</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03205227924205539</v>
+        <v>0.03957942973972763</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.1506938683538078</v>
+        <v>0.255443510100767</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.00848032215218711</v>
+        <v>0.01047321726933114</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.135562990521807</v>
+        <v>0.2367601799698251</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.004709312534274701</v>
+        <v>0.005816533952830424</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.136494594845173</v>
+        <v>0.2379117501251732</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.009898579598035839</v>
+        <v>0.01222457206705313</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.1515887497141231</v>
+        <v>0.2565518738946794</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.00388617955492248</v>
+        <v>0.004799329067655611</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.1494532111534595</v>
+        <v>0.2539160276057623</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.002765245827088388</v>
+        <v>0.003417271308183911</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.1510976279799475</v>
+        <v>0.2559480277661879</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001085386632673013</v>
+        <v>0.00134202806925483</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.1505006319084733</v>
+        <v>0.255212149113805</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0006146480931378066</v>
+        <v>0.0007595409308366967</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.1506425474028008</v>
+        <v>0.2553884179824276</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0002310482153670261</v>
+        <v>0.000286243569209067</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.1504895003816341</v>
+        <v>0.2552007530010878</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001050960443416172</v>
+        <v>0.0001315190949836053</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.1504695780567941</v>
+        <v>0.2551773404545458</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>3.536626471769872e-05</v>
+        <v>4.505416824994641e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.1504348281991135</v>
+        <v>0.2551358151760607</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>6.924643791475056e-06</v>
+        <v>9.78655830142907e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.1504129420253157</v>
+        <v>0.2551102864337202</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>1.200814771567029e-06</v>
+        <v>2.154786274885033e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.1504079323449694</v>
+        <v>0.2551052752640897</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-1.917859128249343e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.1504034053429216</v>
+        <v>0.255100856930037</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-2.908363659633048e-06</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.1503996885124419</v>
+        <v>0.2550973228327851</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.1503943926824378</v>
+        <v>0.2550920270027809</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.1503887306854341</v>
+        <v>0.2550863650057772</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.1503885469429749</v>
+        <v>0.2550861812633181</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.1503885836914666</v>
+        <v>0.2550862180118098</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.1503886939369422</v>
+        <v>0.2550863282572853</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.1503887674339258</v>
+        <v>0.2550864017542689</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.1503889511763849</v>
+        <v>0.2550865854967281</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.1503904946130414</v>
+        <v>0.2550881289333846</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.1503919645527145</v>
+        <v>0.2550895988730577</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.1503932140014365</v>
+        <v>0.2550908483217796</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.1503945736956338</v>
+        <v>0.2550922080159769</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.1503923687861245</v>
+        <v>0.2550900031064677</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.1503919645527145</v>
+        <v>0.2550895988730577</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.1503911193374025</v>
+        <v>0.2550887536577456</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.1503916705647798</v>
+        <v>0.2550893048851229</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.1503913398283534</v>
+        <v>0.2550889741486965</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.1503910458404189</v>
+        <v>0.255088680160762</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.1503911193374025</v>
+        <v>0.2550887536577456</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.1503906783555006</v>
+        <v>0.2550883126758437</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.150390568110025</v>
+        <v>0.2550882024303682</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.1503905313615333</v>
+        <v>0.2550881656818765</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.1503906783555006</v>
+        <v>0.2550883126758437</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.1503902006251069</v>
+        <v>0.2550878349454501</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.1503911560858942</v>
+        <v>0.2550887904062373</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.1503911193374025</v>
+        <v>0.2550887536577456</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.1503907886009761</v>
+        <v>0.2550884229213193</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.1503912295828781</v>
+        <v>0.2550888639032212</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.1503906048585169</v>
+        <v>0.2550882391788601</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.1503904211160578</v>
+        <v>0.255088055436401</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.1503900168826477</v>
+        <v>0.2550876512029909</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.1503891716673358</v>
+        <v>0.2550868059876789</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.1503891349188441</v>
+        <v>0.2550867692391872</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.1503892819128113</v>
+        <v>0.2550869162331545</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.1503892084158277</v>
+        <v>0.2550868427361709</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.1503892819128113</v>
+        <v>0.2550869162331545</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.1503893186613033</v>
+        <v>0.2550869529816464</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.1503892084158277</v>
+        <v>0.2550868427361709</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.1503896493977297</v>
+        <v>0.2550872837180728</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.1503895391522541</v>
+        <v>0.2550871734725972</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.1503895024037622</v>
+        <v>0.2550871367241053</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.1503894289067786</v>
+        <v>0.2550870632271217</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.1503893921582869</v>
+        <v>0.25508702647863</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.1503891716673358</v>
+        <v>0.2550868059876789</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.1503890981703522</v>
+        <v>0.2550867324906953</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.1503890246733685</v>
+        <v>0.2550866589937117</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.1503890614218605</v>
+        <v>0.2550866957422036</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.1503889511763849</v>
+        <v>0.2550865854967281</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.1503890614218605</v>
+        <v>0.2550866957422036</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.173053370802809</v>
+        <v>-0.6386651685504979</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.150389355409795</v>
+        <v>0.2550869897301381</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.01044697407633066</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-1.28</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.005618822760879993</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.8599999999999997</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.002725645899772644</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.001363137736916542</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.0009401161223649979</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.000753156840801239</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.0005346797406673431</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.0003579705953598022</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.0001321658492088318</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.0740314606762852</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>6.921030580997467e-05</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.9867280899030685</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0003300290554761887</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.699424719129852</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.0004856642335653305</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.699424719129852</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.0006143078207969666</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.699424719129852</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.000677693635225296</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.699424719129852</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.0007472969591617584</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.699424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.0006647296249866486</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.699424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.0006138831377029419</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.699424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.0006507374346256256</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.699424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.0007678791880607605</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.699424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.0009152591228485107</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.001024551689624786</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.001166576519608498</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.001270556822419167</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.001404743641614914</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.001427233219146729</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.001455698162317276</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.001475254073739052</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.001534720882773399</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.001601234078407288</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.00167086161673069</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.499424719129852</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.001833399757742882</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.499424719129852</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.001614745706319809</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.499424719129852</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.001447521150112152</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.001339392736554146</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.001223629340529442</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.3</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.001254083588719368</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.3</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.00120975635945797</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.3</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.001184722408652306</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.3</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.001275723800063133</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.3</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.001264277845621109</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.3</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.001172704622149467</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.001062393188476562</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.0009622946381568909</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.499424719129852</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.0004815403372049332</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7867280899030684</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001179446991757723</v>
+        <v>-8.038386143534444e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1354958059853739</v>
+        <v>-0.09234561764556547</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.0004153549671173096</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.0740314606762852</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.0008160844445228577</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.001180252060294151</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.001229973509907722</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.001189412549138069</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.001024233177304268</v>
       </c>
       <c r="JB51" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.0008667409420013428</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>-0.0006277337670326233</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0005381163209676743</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>-0.0004991218447685242</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.0005452092736959457</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>-0.0006233006715774536</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>-0.0006763935089111328</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1356137506845497</v>
+        <v>-0.09242600150700088</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>-0.0006670095026493073</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1356862638100479</v>
+        <v>-0.09249386541326216</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.2607404283618791</v>
+        <v>0.2440231515484895</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>-0.0010871272534132</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.3862957385630379</v>
+        <v>0.3960209710705117</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.01857770077678691</v>
+        <v>0.01738659831372416</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>-0.001355858519673347</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.1622920145064818</v>
+        <v>0.1863795762300433</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.03257908566728022</v>
+        <v>0.03049004114144887</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>-0.001490084454417229</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.2088662120571597</v>
+        <v>0.2299675148270323</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.03957942973972763</v>
+        <v>0.03704211092811067</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>-0.001865435391664505</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.255443510100767</v>
+        <v>0.2735585377344215</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01047321726933114</v>
+        <v>0.009801325028875854</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.002190124243497849</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.2367601799698251</v>
+        <v>0.2560728948845177</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.005816533952830424</v>
+        <v>0.005443424548366816</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>-0.002010256052017212</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.2379117501251732</v>
+        <v>0.2571503046163819</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01222457206705313</v>
+        <v>0.01143999276504531</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>-0.002245010808110237</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.2565518738946794</v>
+        <v>0.2745943394724466</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.004799329067655611</v>
+        <v>0.004491716367079728</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>-0.002673974260687828</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.2539160276057623</v>
+        <v>0.2721272511824546</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.003417271308183911</v>
+        <v>0.003196479610881724</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.003365647047758102</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.2559480277661879</v>
+        <v>0.2740283464565771</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.00134202806925483</v>
+        <v>0.001255123032528712</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.003773043863475323</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.255212149113805</v>
+        <v>0.27333925378072</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.0007595409308366967</v>
+        <v>0.0007102157094923938</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.004168846644461155</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.2553884179824276</v>
+        <v>0.2735040116260843</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.000286243569209067</v>
+        <v>0.0002674536615181594</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.00435322243720293</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.2552007530010878</v>
+        <v>0.2733277639973322</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001315190949836053</v>
+        <v>0.000122711411436276</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.00438707135617733</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.2551773404545458</v>
+        <v>0.2733054658600348</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>4.505416824994641e-05</v>
+        <v>4.182486707253051e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004216937348246574</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.2551358151760607</v>
+        <v>0.2732660030631952</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>9.78655830142907e-06</v>
+        <v>8.832586798111064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.00385588314384222</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.2551102864337202</v>
+        <v>0.273241468019418</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.003469024784862995</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.2551052752640897</v>
+        <v>0.2732364568497871</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>-8.904788376657899e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.003107885830104351</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.255100856930037</v>
+        <v>0.2732320025559829</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.00298302061855793</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.2550973228327851</v>
+        <v>0.2732284684587309</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.002928609028458595</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.2550920270027809</v>
+        <v>0.2732231726287268</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.002789845690131187</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.2550863650057772</v>
+        <v>0.2732175106317231</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.002571478486061096</v>
       </c>
       <c r="JB80" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.2550861812633181</v>
+        <v>0.2732173268892639</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.002331567928195</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.3</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.2550862180118098</v>
+        <v>0.2732173636377556</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.002167807891964912</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.2550863282572853</v>
+        <v>0.2732174738832311</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.002107651904225349</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.2550864017542689</v>
+        <v>0.2732175473802148</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.001939935609698296</v>
       </c>
       <c r="JB84" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.2550865854967281</v>
+        <v>0.2732177311226739</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001990903168916702</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.2550881289333846</v>
+        <v>0.2732192745593304</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.002763936296105385</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.16</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.2550895988730577</v>
+        <v>0.2732207444990035</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.003742584027349949</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.2550908483217796</v>
+        <v>0.2732219939477255</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0</v>
+        <v>-0.0042838454246521</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.2550922080159769</v>
+        <v>0.2732233536419228</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.005727583542466164</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.2550900031064677</v>
+        <v>0.2732211487324135</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.006774826906621456</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.2550895988730577</v>
+        <v>0.2732207444990035</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.007311971858143806</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.2550887536577456</v>
+        <v>0.2732198992836916</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.007722198963165283</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.2550893048851229</v>
+        <v>0.2732204505110688</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.007891256362199783</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.2550889741486965</v>
+        <v>0.2732201197746424</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.007697822526097298</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.255088680160762</v>
+        <v>0.2732198257867079</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.007542955689132214</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.2550887536577456</v>
+        <v>0.2732198992836916</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.00722750648856163</v>
       </c>
       <c r="JB96" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.2550883126758437</v>
+        <v>0.2732194583017896</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.00686312559992075</v>
       </c>
       <c r="JB97" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.2550882024303682</v>
+        <v>0.273219348056314</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.006451471708714962</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.2550881656818765</v>
+        <v>0.2732193113078223</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.006223768927156925</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.2550883126758437</v>
+        <v>0.2732194583017896</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.005557304248213768</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.2550878349454501</v>
+        <v>0.2732189805713959</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.00529320165514946</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.2550887904062373</v>
+        <v>0.2732199360321833</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.005718869157135487</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.2550887536577456</v>
+        <v>0.2732198992836916</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.006059818901121616</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.2550884229213193</v>
+        <v>0.2732195685472651</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.006333389319479465</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.2550888639032212</v>
+        <v>0.2732200095291671</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.006429471075534821</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.2550882391788601</v>
+        <v>0.273219384804806</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.006292317993938923</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.255088055436401</v>
+        <v>0.2732192010623468</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.006050118245184422</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.2550876512029909</v>
+        <v>0.2732187968289368</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.005556418560445309</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.16</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.2550868059876789</v>
+        <v>0.2732179516136248</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.004914735443890095</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.2550867692391872</v>
+        <v>0.2732179148651331</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.004376368597149849</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.2550869162331545</v>
+        <v>0.2732180618591004</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.003972627222537994</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.2550868427361709</v>
+        <v>0.2732179883621167</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.003528375178575516</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.2550869162331545</v>
+        <v>0.2732180618591004</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.003505491651594639</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.2550869529816464</v>
+        <v>0.2732180986075923</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.003331590443849564</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.2550868427361709</v>
+        <v>0.2732179883621167</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.003464513458311558</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.2550872837180728</v>
+        <v>0.2732184293440187</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.003544595092535019</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.2550871734725972</v>
+        <v>0.2732183190985432</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.003640587441623211</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.2550871367241053</v>
+        <v>0.2732182823500512</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.003642803989350796</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.16</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.2550870632271217</v>
+        <v>0.2732182088530676</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.003613178618252277</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.16</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.25508702647863</v>
+        <v>0.2732181721045759</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.003526740707457066</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.6386651685504979</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.2550868059876789</v>
+        <v>0.2732179516136248</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.003323067910969257</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.2550867324906953</v>
+        <v>0.2732178781166412</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.003132747486233711</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.2550866589937117</v>
+        <v>0.2732178046196576</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.003007899969816208</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.2550866957422036</v>
+        <v>0.2732178413681495</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.002811696380376816</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.2550865854967281</v>
+        <v>0.2732177311226739</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.002593589946627617</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.2550866957422036</v>
+        <v>0.2732178413681495</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.002603599801659584</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6386651685504979</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.2550869897301381</v>
+        <v>0.273218135356084</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-Mamba1_repeat_2_000008.xlsx
+++ b/out/LSTM-Mamba1_repeat_2_000008.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.01044697407633066</v>
+        <v>-0.01044696755707264</v>
       </c>
       <c r="JB2" t="n">
         <v>-1.28</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.005618822760879993</v>
+        <v>-0.005618821829557419</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.8599999999999997</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.002725645899772644</v>
+        <v>-0.002725642174482346</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.4399999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.001363137736916542</v>
+        <v>-0.001363132148981094</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.16</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.0009401161223649979</v>
+        <v>-0.0009401030838489532</v>
       </c>
       <c r="JB6" t="n">
         <v>0.7199999999999999</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.000753156840801239</v>
+        <v>-0.0007531475275754929</v>
       </c>
       <c r="JB7" t="n">
         <v>0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.0005346797406673431</v>
+        <v>-0.0005346573889255524</v>
       </c>
       <c r="JB8" t="n">
         <v>0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.0003579705953598022</v>
+        <v>-0.0003579407930374146</v>
       </c>
       <c r="JB9" t="n">
         <v>0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.0001321658492088318</v>
+        <v>-0.0001321509480476379</v>
       </c>
       <c r="JB10" t="n">
         <v>0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>6.921030580997467e-05</v>
+        <v>6.925314664840698e-05</v>
       </c>
       <c r="JB11" t="n">
         <v>0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.0003300290554761887</v>
+        <v>0.0003300569951534271</v>
       </c>
       <c r="JB12" t="n">
         <v>0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.0004856642335653305</v>
+        <v>0.0004856809973716736</v>
       </c>
       <c r="JB13" t="n">
         <v>0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.0006143078207969666</v>
+        <v>0.0006143394857645035</v>
       </c>
       <c r="JB14" t="n">
         <v>0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.000677693635225296</v>
+        <v>0.0006777346134185791</v>
       </c>
       <c r="JB15" t="n">
         <v>0.9999999999999998</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.0007472969591617584</v>
+        <v>0.0007473360747098923</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3999999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.0006647296249866486</v>
+        <v>0.0006647650152444839</v>
       </c>
       <c r="JB17" t="n">
         <v>0.3999999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.0006138831377029419</v>
+        <v>0.000613899901509285</v>
       </c>
       <c r="JB18" t="n">
         <v>0.3999999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.0006507374346256256</v>
+        <v>0.0006507355719804764</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3999999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.0007678791880607605</v>
+        <v>0.0007678847759962082</v>
       </c>
       <c r="JB20" t="n">
         <v>0.3999999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.0009152591228485107</v>
+        <v>0.0009152758866548538</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3999999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.001024551689624786</v>
+        <v>0.001024585217237473</v>
       </c>
       <c r="JB22" t="n">
         <v>0.3999999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.001166576519608498</v>
+        <v>0.001166615635156631</v>
       </c>
       <c r="JB23" t="n">
         <v>0.3999999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.001270556822419167</v>
+        <v>0.001270592212677002</v>
       </c>
       <c r="JB24" t="n">
         <v>0.3999999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.001404743641614914</v>
+        <v>0.001404765993356705</v>
       </c>
       <c r="JB25" t="n">
         <v>0.3999999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.001427233219146729</v>
+        <v>0.001427238807082176</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3999999999999999</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0.001455698162317276</v>
+        <v>0.001455673947930336</v>
       </c>
       <c r="JB27" t="n">
         <v>0.3999999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.001475254073739052</v>
+        <v>0.001475246623158455</v>
       </c>
       <c r="JB28" t="n">
         <v>0.3999999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.001534720882773399</v>
+        <v>0.001534733921289444</v>
       </c>
       <c r="JB29" t="n">
         <v>0.3999999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.001601234078407288</v>
+        <v>0.001601260155439377</v>
       </c>
       <c r="JB30" t="n">
         <v>0.3999999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.00167086161673069</v>
+        <v>0.001670902594923973</v>
       </c>
       <c r="JB31" t="n">
         <v>0.3999999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.001833399757742882</v>
+        <v>0.00183340348303318</v>
       </c>
       <c r="JB32" t="n">
         <v>0.2599999999999998</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.001614745706319809</v>
+        <v>0.001614764332771301</v>
       </c>
       <c r="JB33" t="n">
         <v>0.1199999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.001447521150112152</v>
+        <v>0.001447552815079689</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.02000000000000007</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.001339392736554146</v>
+        <v>0.001339413225650787</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.001223629340529442</v>
+        <v>0.00122365728020668</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.3</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.001254083588719368</v>
+        <v>0.00125410407781601</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.3</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.00120975635945797</v>
+        <v>0.001209819689393044</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.3</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.001184722408652306</v>
+        <v>0.001184763386845589</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.3</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.001275723800063133</v>
+        <v>0.001275751739740372</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.3</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.001264277845621109</v>
+        <v>0.001264289021492004</v>
       </c>
       <c r="JB41" t="n">
         <v>-0.3</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.001172704622149467</v>
+        <v>0.0011727474629879</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.4399999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.001062393188476562</v>
+        <v>0.001062424853444099</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.5799999999999998</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.0009622946381568909</v>
+        <v>0.0009623020887374878</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.7199999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.0004815403372049332</v>
+        <v>0.0004815272986888885</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.8599999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.0004153549671173096</v>
+        <v>-0.0004153531044721603</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.0008160844445228577</v>
+        <v>-0.0008160769939422607</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.001180252060294151</v>
+        <v>-0.001180248335003853</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.001229973509907722</v>
+        <v>-0.001229962334036827</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.001189412549138069</v>
+        <v>-0.001189397647976875</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.9999999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.001024233177304268</v>
+        <v>-0.001024218276143074</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.9999999999999998</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.0008667409420013428</v>
+        <v>-0.0008667279034852982</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.9999999999999998</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>-0.0006277337670326233</v>
+        <v>-0.0006277468055486679</v>
       </c>
       <c r="JB53" t="n">
         <v>-0.9999999999999998</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0005381163209676743</v>
+        <v>-0.0005381088703870773</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.9999999999999998</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>-0.0004991218447685242</v>
+        <v>-0.0004991162568330765</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.9999999999999998</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.0005452092736959457</v>
+        <v>-0.0005451943725347519</v>
       </c>
       <c r="JB56" t="n">
         <v>-0.9999999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>-0.0006233006715774536</v>
+        <v>-0.0006232894957065582</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>-0.0006763935089111328</v>
+        <v>-0.0006763823330402374</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>-0.0006670095026493073</v>
+        <v>-0.0006670542061328888</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>-0.0010871272534132</v>
+        <v>-0.001087132841348648</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.9999999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>-0.001355858519673347</v>
+        <v>-0.001355862244963646</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.9999999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>-0.001490084454417229</v>
+        <v>-0.00149008072912693</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.9999999999999998</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>-0.001865435391664505</v>
+        <v>-0.001865455880761147</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>-0.002190124243497849</v>
+        <v>-0.002190133556723595</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>-0.002010256052017212</v>
+        <v>-0.00201026163995266</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.9999999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>-0.002245010808110237</v>
+        <v>-0.002245018258690834</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.9999999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>-0.002673974260687828</v>
+        <v>-0.002673972398042679</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.9999999999999998</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>-0.003365647047758102</v>
+        <v>-0.003365644253790379</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.9999999999999998</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>-0.003773043863475323</v>
+        <v>-0.0037730373442173</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.9999999999999998</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>-0.004168846644461155</v>
+        <v>-0.004168841056525707</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>-0.00435322243720293</v>
+        <v>-0.004353256896138191</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>-0.00438707135617733</v>
+        <v>-0.004387080669403076</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.9999999999999998</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>-0.004216937348246574</v>
+        <v>-0.004216932691633701</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>-0.00385588314384222</v>
+        <v>-0.003855888731777668</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>-0.003469024784862995</v>
+        <v>-0.003469022922217846</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.9999999999999998</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>-0.003107885830104351</v>
+        <v>-0.003107890486717224</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.9999999999999998</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>-0.00298302061855793</v>
+        <v>-0.002983028069138527</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>-0.002928609028458595</v>
+        <v>-0.002928620204329491</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.9999999999999998</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>-0.002789845690131187</v>
+        <v>-0.002789843827486038</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.2599999999999998</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>-0.002571478486061096</v>
+        <v>-0.002571480348706245</v>
       </c>
       <c r="JB80" t="n">
         <v>0.02000000000000007</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>-0.002331567928195</v>
+        <v>-0.002331564202904701</v>
       </c>
       <c r="JB81" t="n">
         <v>0.3</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>-0.002167807891964912</v>
+        <v>-0.002167804166674614</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>-0.002107651904225349</v>
+        <v>-0.0021076500415802</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>-0.001939935609698296</v>
+        <v>-0.001939943060278893</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>-0.001990903168916702</v>
+        <v>-0.001990929245948792</v>
       </c>
       <c r="JB85" t="n">
         <v>0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>-0.002763936296105385</v>
+        <v>-0.002763980999588966</v>
       </c>
       <c r="JB86" t="n">
         <v>0.16</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>-0.003742584027349949</v>
+        <v>-0.00374263059347868</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>-0.0042838454246521</v>
+        <v>-0.004283903166651726</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.9999999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>-0.005727583542466164</v>
+        <v>-0.005727597512304783</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.9999999999999998</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>-0.006774826906621456</v>
+        <v>-0.006774852052330971</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.9999999999999998</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>-0.007311971858143806</v>
+        <v>-0.007312017492949963</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>-0.007722198963165283</v>
+        <v>-0.00772232748568058</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>-0.007891256362199783</v>
+        <v>-0.007891284301877022</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>-0.007697822526097298</v>
+        <v>-0.007697856053709984</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>-0.007542955689132214</v>
+        <v>-0.007542993873357773</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>-0.00722750648856163</v>
+        <v>-0.00722754281014204</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>-0.00686312559992075</v>
+        <v>-0.006863178685307503</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>-0.006451471708714962</v>
+        <v>-0.0064514996483922</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>-0.006223768927156925</v>
+        <v>-0.006223775446414948</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>-0.005557304248213768</v>
+        <v>-0.005557291209697723</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>-0.00529320165514946</v>
+        <v>-0.005293234251439571</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>-0.005718869157135487</v>
+        <v>-0.005718875676393509</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.9999999999999998</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>-0.006059818901121616</v>
+        <v>-0.006059823557734489</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.9999999999999998</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>-0.006333389319479465</v>
+        <v>-0.006333444267511368</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.9999999999999998</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>-0.006429471075534821</v>
+        <v>-0.006429489701986313</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.9999999999999998</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>-0.006292317993938923</v>
+        <v>-0.006292332895100117</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>-0.006050118245184422</v>
+        <v>-0.00605014618486166</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.1199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>-0.005556418560445309</v>
+        <v>-0.005556375719606876</v>
       </c>
       <c r="JB108" t="n">
         <v>0.16</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>-0.004914735443890095</v>
+        <v>-0.004914714954793453</v>
       </c>
       <c r="JB109" t="n">
         <v>0.4399999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>-0.004376368597149849</v>
+        <v>-0.004376380704343319</v>
       </c>
       <c r="JB110" t="n">
         <v>0.7199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>-0.003972627222537994</v>
+        <v>-0.003972649574279785</v>
       </c>
       <c r="JB111" t="n">
         <v>0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>-0.003528375178575516</v>
+        <v>-0.003528408706188202</v>
       </c>
       <c r="JB112" t="n">
         <v>0.9999999999999998</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>-0.003505491651594639</v>
+        <v>-0.00350551214069128</v>
       </c>
       <c r="JB113" t="n">
         <v>0.9999999999999998</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>-0.003331590443849564</v>
+        <v>-0.003331602551043034</v>
       </c>
       <c r="JB114" t="n">
         <v>0.9999999999999998</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>-0.003464513458311558</v>
+        <v>-0.003464519046247005</v>
       </c>
       <c r="JB115" t="n">
         <v>0.8599999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>-0.003544595092535019</v>
+        <v>-0.003544616512954235</v>
       </c>
       <c r="JB116" t="n">
         <v>0.7199999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>-0.003640587441623211</v>
+        <v>-0.003640593960881233</v>
       </c>
       <c r="JB117" t="n">
         <v>-0.02000000000000007</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>-0.003642803989350796</v>
+        <v>-0.003642802126705647</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.16</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>-0.003613178618252277</v>
+        <v>-0.003613181412220001</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.16</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>-0.003526740707457066</v>
+        <v>-0.003526744432747364</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.02000000000000007</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>-0.003323067910969257</v>
+        <v>-0.003323101438581944</v>
       </c>
       <c r="JB121" t="n">
         <v>0.1199999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>-0.003132747486233711</v>
+        <v>-0.003132782876491547</v>
       </c>
       <c r="JB122" t="n">
         <v>0.2599999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>-0.003007899969816208</v>
+        <v>-0.0030079185962677</v>
       </c>
       <c r="JB123" t="n">
         <v>0.9999999999999998</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>-0.002811696380376816</v>
+        <v>-0.002811705693602562</v>
       </c>
       <c r="JB124" t="n">
         <v>0.9999999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>-0.002593589946627617</v>
+        <v>-0.002593604847788811</v>
       </c>
       <c r="JB125" t="n">
         <v>0.9999999999999996</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>-0.002603599801659584</v>
+        <v>-0.00260360911488533</v>
       </c>
       <c r="JB126" t="n">
         <v>0.9999999999999996</v>
